--- a/diseases/d003/2015-2019.xlsx
+++ b/diseases/d003/2015-2019.xlsx
@@ -1061,9 +1061,6 @@
       <c r="O4" t="n">
         <v>0</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
@@ -1457,9 +1454,6 @@
       <c r="O6" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
@@ -2493,9 +2487,6 @@
       <c r="O13" t="n">
         <v>0</v>
       </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
       <c r="R13" t="n">
         <v>0</v>
       </c>
@@ -3529,9 +3520,6 @@
       <c r="O20" t="n">
         <v>0</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>0</v>
       </c>
@@ -4565,9 +4553,6 @@
       <c r="O27" t="n">
         <v>0</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
       <c r="R27" t="n">
         <v>0</v>
       </c>
@@ -5749,9 +5734,6 @@
       <c r="O35" t="n">
         <v>0</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
       <c r="R35" t="n">
         <v>0</v>
       </c>
@@ -6785,9 +6767,6 @@
       <c r="O42" t="n">
         <v>0</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" t="n">
         <v>0</v>
       </c>
@@ -7821,9 +7800,6 @@
       <c r="O49" t="n">
         <v>0</v>
       </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
       <c r="R49" t="n">
         <v>0</v>
       </c>
@@ -9005,9 +8981,6 @@
       <c r="O57" t="n">
         <v>0</v>
       </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
       <c r="R57" t="n">
         <v>0</v>
       </c>
@@ -10041,9 +10014,6 @@
       <c r="O64" t="n">
         <v>0</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
         <v>0</v>
       </c>
@@ -11077,9 +11047,6 @@
       <c r="O71" t="n">
         <v>0</v>
       </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
       <c r="R71" t="n">
         <v>0</v>
       </c>
@@ -12261,9 +12228,6 @@
       <c r="O79" t="n">
         <v>0</v>
       </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
       <c r="R79" t="n">
         <v>0</v>
       </c>
@@ -13297,9 +13261,6 @@
       <c r="O86" t="n">
         <v>0</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>0</v>
       </c>
@@ -14333,9 +14294,6 @@
       <c r="O93" t="n">
         <v>0</v>
       </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
       <c r="R93" t="n">
         <v>0</v>
       </c>
@@ -14877,9 +14835,6 @@
       <c r="O96" t="n">
         <v>0</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="R96" t="n">
         <v>0</v>
       </c>
@@ -15913,9 +15868,6 @@
       <c r="O103" t="n">
         <v>0</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
       <c r="R103" t="n">
         <v>0</v>
       </c>
@@ -16949,9 +16901,6 @@
       <c r="O110" t="n">
         <v>0</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="R110" t="n">
         <v>0</v>
       </c>
@@ -18133,9 +18082,6 @@
       <c r="O118" t="n">
         <v>0</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="R118" t="n">
         <v>0</v>
       </c>
@@ -19169,9 +19115,6 @@
       <c r="O125" t="n">
         <v>0</v>
       </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
       <c r="R125" t="n">
         <v>0</v>
       </c>
@@ -20205,9 +20148,6 @@
       <c r="O132" t="n">
         <v>0</v>
       </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
       <c r="R132" t="n">
         <v>0</v>
       </c>
@@ -21389,9 +21329,6 @@
       <c r="O140" t="n">
         <v>0</v>
       </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
       <c r="R140" t="n">
         <v>0</v>
       </c>
@@ -22425,9 +22362,6 @@
       <c r="O147" t="n">
         <v>0</v>
       </c>
-      <c r="Q147" t="n">
-        <v>0</v>
-      </c>
       <c r="R147" t="n">
         <v>0</v>
       </c>
@@ -23461,9 +23395,6 @@
       <c r="O154" t="n">
         <v>0</v>
       </c>
-      <c r="Q154" t="n">
-        <v>0</v>
-      </c>
       <c r="R154" t="n">
         <v>0</v>
       </c>
@@ -24645,9 +24576,6 @@
       <c r="O162" t="n">
         <v>0</v>
       </c>
-      <c r="Q162" t="n">
-        <v>0</v>
-      </c>
       <c r="R162" t="n">
         <v>0</v>
       </c>
@@ -25681,9 +25609,6 @@
       <c r="O169" t="n">
         <v>0</v>
       </c>
-      <c r="Q169" t="n">
-        <v>0</v>
-      </c>
       <c r="R169" t="n">
         <v>0</v>
       </c>
@@ -26717,9 +26642,6 @@
       <c r="O176" t="n">
         <v>0</v>
       </c>
-      <c r="Q176" t="n">
-        <v>0</v>
-      </c>
       <c r="R176" t="n">
         <v>0</v>
       </c>
@@ -27901,9 +27823,6 @@
       <c r="O184" t="n">
         <v>0</v>
       </c>
-      <c r="Q184" t="n">
-        <v>0</v>
-      </c>
       <c r="R184" t="n">
         <v>0</v>
       </c>
@@ -28297,9 +28216,6 @@
       <c r="O186" t="n">
         <v>0</v>
       </c>
-      <c r="Q186" t="n">
-        <v>0</v>
-      </c>
       <c r="R186" t="n">
         <v>0</v>
       </c>
@@ -29333,9 +29249,6 @@
       <c r="O193" t="n">
         <v>0</v>
       </c>
-      <c r="Q193" t="n">
-        <v>0</v>
-      </c>
       <c r="R193" t="n">
         <v>0</v>
       </c>
@@ -30369,9 +30282,6 @@
       <c r="O200" t="n">
         <v>0</v>
       </c>
-      <c r="Q200" t="n">
-        <v>0</v>
-      </c>
       <c r="R200" t="n">
         <v>0</v>
       </c>
@@ -31553,9 +31463,6 @@
       <c r="O208" t="n">
         <v>0</v>
       </c>
-      <c r="Q208" t="n">
-        <v>0</v>
-      </c>
       <c r="R208" t="n">
         <v>0</v>
       </c>
@@ -32589,9 +32496,6 @@
       <c r="O215" t="n">
         <v>0</v>
       </c>
-      <c r="Q215" t="n">
-        <v>0</v>
-      </c>
       <c r="R215" t="n">
         <v>0</v>
       </c>
@@ -33625,9 +33529,6 @@
       <c r="O222" t="n">
         <v>0</v>
       </c>
-      <c r="Q222" t="n">
-        <v>0</v>
-      </c>
       <c r="R222" t="n">
         <v>0</v>
       </c>
@@ -34809,9 +34710,6 @@
       <c r="O230" t="n">
         <v>0</v>
       </c>
-      <c r="Q230" t="n">
-        <v>0</v>
-      </c>
       <c r="R230" t="n">
         <v>0</v>
       </c>
@@ -35845,9 +35743,6 @@
       <c r="O237" t="n">
         <v>0</v>
       </c>
-      <c r="Q237" t="n">
-        <v>0</v>
-      </c>
       <c r="R237" t="n">
         <v>0</v>
       </c>
@@ -37029,9 +36924,6 @@
       <c r="O245" t="n">
         <v>0</v>
       </c>
-      <c r="Q245" t="n">
-        <v>0</v>
-      </c>
       <c r="R245" t="n">
         <v>0</v>
       </c>
@@ -38065,9 +37957,6 @@
       <c r="O252" t="n">
         <v>0</v>
       </c>
-      <c r="Q252" t="n">
-        <v>0</v>
-      </c>
       <c r="R252" t="n">
         <v>0</v>
       </c>
@@ -39101,9 +38990,6 @@
       <c r="O259" t="n">
         <v>0</v>
       </c>
-      <c r="Q259" t="n">
-        <v>0</v>
-      </c>
       <c r="R259" t="n">
         <v>0</v>
       </c>
@@ -40285,9 +40171,6 @@
       <c r="O267" t="n">
         <v>0</v>
       </c>
-      <c r="Q267" t="n">
-        <v>0</v>
-      </c>
       <c r="R267" t="n">
         <v>0</v>
       </c>
@@ -41321,9 +41204,6 @@
       <c r="O274" t="n">
         <v>0</v>
       </c>
-      <c r="Q274" t="n">
-        <v>0</v>
-      </c>
       <c r="R274" t="n">
         <v>0</v>
       </c>
@@ -41717,9 +41597,6 @@
       <c r="O276" t="n">
         <v>0</v>
       </c>
-      <c r="Q276" t="n">
-        <v>0</v>
-      </c>
       <c r="R276" t="n">
         <v>0</v>
       </c>
@@ -42753,9 +42630,6 @@
       <c r="O283" t="n">
         <v>0</v>
       </c>
-      <c r="Q283" t="n">
-        <v>0</v>
-      </c>
       <c r="R283" t="n">
         <v>0</v>
       </c>
@@ -43789,9 +43663,6 @@
       <c r="O290" t="n">
         <v>0</v>
       </c>
-      <c r="Q290" t="n">
-        <v>0</v>
-      </c>
       <c r="R290" t="n">
         <v>0</v>
       </c>
@@ -44973,9 +44844,6 @@
       <c r="O298" t="n">
         <v>0</v>
       </c>
-      <c r="Q298" t="n">
-        <v>0</v>
-      </c>
       <c r="R298" t="n">
         <v>0</v>
       </c>
@@ -46009,9 +45877,6 @@
       <c r="O305" t="n">
         <v>0</v>
       </c>
-      <c r="Q305" t="n">
-        <v>0</v>
-      </c>
       <c r="R305" t="n">
         <v>0</v>
       </c>
@@ -47193,9 +47058,6 @@
       <c r="O313" t="n">
         <v>0</v>
       </c>
-      <c r="Q313" t="n">
-        <v>0</v>
-      </c>
       <c r="R313" t="n">
         <v>0</v>
       </c>
@@ -48229,9 +48091,6 @@
       <c r="O320" t="n">
         <v>0</v>
       </c>
-      <c r="Q320" t="n">
-        <v>0</v>
-      </c>
       <c r="R320" t="n">
         <v>0</v>
       </c>
@@ -49265,9 +49124,6 @@
       <c r="O327" t="n">
         <v>0</v>
       </c>
-      <c r="Q327" t="n">
-        <v>0</v>
-      </c>
       <c r="R327" t="n">
         <v>0</v>
       </c>
@@ -50449,9 +50305,6 @@
       <c r="O335" t="n">
         <v>0</v>
       </c>
-      <c r="Q335" t="n">
-        <v>0</v>
-      </c>
       <c r="R335" t="n">
         <v>0</v>
       </c>
@@ -51485,9 +51338,6 @@
       <c r="O342" t="n">
         <v>0</v>
       </c>
-      <c r="Q342" t="n">
-        <v>0</v>
-      </c>
       <c r="R342" t="n">
         <v>0</v>
       </c>
@@ -52521,9 +52371,6 @@
       <c r="O349" t="n">
         <v>0</v>
       </c>
-      <c r="Q349" t="n">
-        <v>0</v>
-      </c>
       <c r="R349" t="n">
         <v>0</v>
       </c>
@@ -53705,9 +53552,6 @@
       <c r="O357" t="n">
         <v>0</v>
       </c>
-      <c r="Q357" t="n">
-        <v>0</v>
-      </c>
       <c r="R357" t="n">
         <v>0</v>
       </c>
@@ -54741,9 +54585,6 @@
       <c r="O364" t="n">
         <v>0</v>
       </c>
-      <c r="Q364" t="n">
-        <v>0</v>
-      </c>
       <c r="R364" t="n">
         <v>0</v>
       </c>
@@ -55137,9 +54978,6 @@
       <c r="O366" t="n">
         <v>0</v>
       </c>
-      <c r="Q366" t="n">
-        <v>0</v>
-      </c>
       <c r="R366" t="n">
         <v>0</v>
       </c>
@@ -56321,9 +56159,6 @@
       <c r="O374" t="n">
         <v>0</v>
       </c>
-      <c r="Q374" t="n">
-        <v>0</v>
-      </c>
       <c r="R374" t="n">
         <v>0</v>
       </c>
@@ -57357,9 +57192,6 @@
       <c r="O381" t="n">
         <v>0</v>
       </c>
-      <c r="Q381" t="n">
-        <v>0</v>
-      </c>
       <c r="R381" t="n">
         <v>0</v>
       </c>
@@ -58393,9 +58225,6 @@
       <c r="O388" t="n">
         <v>0</v>
       </c>
-      <c r="Q388" t="n">
-        <v>0</v>
-      </c>
       <c r="R388" t="n">
         <v>0</v>
       </c>
@@ -59429,9 +59258,6 @@
       <c r="O395" t="n">
         <v>0</v>
       </c>
-      <c r="Q395" t="n">
-        <v>0</v>
-      </c>
       <c r="R395" t="n">
         <v>0</v>
       </c>
@@ -60613,9 +60439,6 @@
       <c r="O403" t="n">
         <v>0</v>
       </c>
-      <c r="Q403" t="n">
-        <v>0</v>
-      </c>
       <c r="R403" t="n">
         <v>0</v>
       </c>
@@ -61649,9 +61472,6 @@
       <c r="O410" t="n">
         <v>0</v>
       </c>
-      <c r="Q410" t="n">
-        <v>0</v>
-      </c>
       <c r="R410" t="n">
         <v>0</v>
       </c>
@@ -62685,9 +62505,6 @@
       <c r="O417" t="n">
         <v>0</v>
       </c>
-      <c r="Q417" t="n">
-        <v>0</v>
-      </c>
       <c r="R417" t="n">
         <v>0</v>
       </c>
@@ -63869,9 +63686,6 @@
       <c r="O425" t="n">
         <v>0</v>
       </c>
-      <c r="Q425" t="n">
-        <v>0</v>
-      </c>
       <c r="R425" t="n">
         <v>0</v>
       </c>
@@ -64905,9 +64719,6 @@
       <c r="O432" t="n">
         <v>0</v>
       </c>
-      <c r="Q432" t="n">
-        <v>0</v>
-      </c>
       <c r="R432" t="n">
         <v>0</v>
       </c>
@@ -66089,9 +65900,6 @@
       <c r="O440" t="n">
         <v>0</v>
       </c>
-      <c r="Q440" t="n">
-        <v>0</v>
-      </c>
       <c r="R440" t="n">
         <v>0</v>
       </c>
@@ -67123,9 +66931,6 @@
         <v>0</v>
       </c>
       <c r="O447" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q447" t="n">
         <v>0</v>
       </c>
       <c r="R447" t="n">
